--- a/exp_m3_out/junyi/module3_full.xlsx
+++ b/exp_m3_out/junyi/module3_full.xlsx
@@ -467,13 +467,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8063164730381653</v>
+        <v>0.8116558705820961</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7696168929769175</v>
+        <v>0.769443858962392</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3990282279691905</v>
+        <v>0.3991104688319904</v>
       </c>
     </row>
     <row r="3">
@@ -486,13 +486,13 @@
         <v>0.1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8063164714802239</v>
+        <v>0.8116558768729586</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7696168929769175</v>
+        <v>0.769443858962392</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3990282279691905</v>
+        <v>0.3991104688319904</v>
       </c>
     </row>
     <row r="4">
@@ -505,13 +505,13 @@
         <v>0.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8063164711513251</v>
+        <v>0.811655868485142</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7696168929769175</v>
+        <v>0.769443858962392</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3990282279691905</v>
+        <v>0.3991104688319904</v>
       </c>
     </row>
     <row r="5">
@@ -524,13 +524,13 @@
         <v>0.3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8063164713936717</v>
+        <v>0.811655868485142</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7696168929769175</v>
+        <v>0.769443858962392</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3990282279691905</v>
+        <v>0.3991104688319904</v>
       </c>
     </row>
     <row r="6">
@@ -543,13 +543,13 @@
         <v>0.4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8063164722418843</v>
+        <v>0.8116558747760043</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7696168929769175</v>
+        <v>0.769443858962392</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3990282279691905</v>
+        <v>0.3991104688319904</v>
       </c>
     </row>
     <row r="7">
@@ -562,13 +562,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.806316471895675</v>
+        <v>0.8116558600973253</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7696168929769175</v>
+        <v>0.769443858962392</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3990282279691905</v>
+        <v>0.3991104688319904</v>
       </c>
     </row>
     <row r="8">
@@ -581,13 +581,13 @@
         <v>0.1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7944669927163273</v>
+        <v>0.7905138315221647</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7519772560928982</v>
+        <v>0.7393634639125591</v>
       </c>
       <c r="E8" t="n">
-        <v>0.409844470734277</v>
+        <v>0.4179171949302755</v>
       </c>
     </row>
     <row r="9">
@@ -600,13 +600,13 @@
         <v>0.2</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7926693508778102</v>
+        <v>0.787976078735495</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7504670038561956</v>
+        <v>0.7373159495347927</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4102017513649266</v>
+        <v>0.4200950088215374</v>
       </c>
     </row>
     <row r="10">
@@ -619,13 +619,13 @@
         <v>0.3</v>
       </c>
       <c r="C10" t="n">
-        <v>0.78799980584227</v>
+        <v>0.7867350928808515</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7417878327743852</v>
+        <v>0.7354490981903586</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4148736422126622</v>
+        <v>0.4221307191424615</v>
       </c>
     </row>
     <row r="11">
@@ -638,13 +638,13 @@
         <v>0.4</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7919432783960942</v>
+        <v>0.7901401081593853</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7495084169934784</v>
+        <v>0.7385203697570082</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4112942303986723</v>
+        <v>0.4194484970056296</v>
       </c>
     </row>
   </sheetData>
@@ -698,13 +698,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8063164708397368</v>
+        <v>0.8116558726790503</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7696168929769175</v>
+        <v>0.769443858962392</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3990282279691905</v>
+        <v>0.3991104688319904</v>
       </c>
     </row>
     <row r="3">
@@ -717,13 +717,13 @@
         <v>0.1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7888902066331068</v>
+        <v>0.7881228193931049</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7440108803705443</v>
+        <v>0.7359007557736894</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4138977874777829</v>
+        <v>0.420800571614229</v>
       </c>
     </row>
     <row r="4">
@@ -736,13 +736,13 @@
         <v>0.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7885523000142929</v>
+        <v>0.7875444500807776</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7438251712347472</v>
+        <v>0.7345758935292523</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4140528731756505</v>
+        <v>0.4212157255033438</v>
       </c>
     </row>
     <row r="5">
@@ -755,13 +755,13 @@
         <v>0.3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7886215045711324</v>
+        <v>0.7879431313918674</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7441091969718486</v>
+        <v>0.7362620818403541</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4140085689042584</v>
+        <v>0.4206609742027072</v>
       </c>
     </row>
     <row r="6">
@@ -774,13 +774,13 @@
         <v>0.4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.788636421445356</v>
+        <v>0.7877119757479367</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7440136113872472</v>
+        <v>0.7356899822348018</v>
       </c>
       <c r="E6" t="n">
-        <v>0.413992947908821</v>
+        <v>0.4211145364022471</v>
       </c>
     </row>
   </sheetData>
